--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25575.32</v>
+        <v>25435.53</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1363.6</v>
+        <v>1348.41</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3028.31</v>
+        <v>2998.18</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13518.38</v>
+        <v>13461.71</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>551.98</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1126.53</v>
+        <v>1138.62</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7593.67</v>
+        <v>7635.2</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1917.81</v>
+        <v>1916.5</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>637.9400000000001</v>
+        <v>634.5700000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4658.95</v>
+        <v>4634.34</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1023.12</v>
+        <v>1017.71</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1033.44</v>
+        <v>1027.98</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5750.99</v>
+        <v>5714.95</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6373.75</v>
+        <v>6333.81</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>441.21</v>
+        <v>447.92</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1795.93</v>
+        <v>1801.14</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13920.4</v>
+        <v>13906.04</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4029.63</v>
+        <v>4007.69</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4434.73</v>
+        <v>4417.62</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>18578.07</v>
+        <v>18506.36</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46398.24</v>
+        <v>46638.46</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1444.83</v>
+        <v>1423.28</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8329.07</v>
+        <v>8423.790000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1827.9</v>
+        <v>1839.59</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9511.74</v>
+        <v>9470.040000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>34315.41</v>
+        <v>34224.65</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>863.97</v>
+        <v>872.62</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3348.98</v>
+        <v>3332.02</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>701426-405-CM25</t>
+          <t>3887-242-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25435.53</v>
+        <v>1649.38</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1091-487-CM25</t>
+          <t>701426-405-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,22 +590,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>1348.41</v>
+        <v>25435.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1091-592-CM25</t>
+          <t>1091-487-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>2998.18</v>
+        <v>1348.41</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1091-604-CM25</t>
+          <t>1091-592-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13461.71</v>
+        <v>2998.18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1091-640-CM25</t>
+          <t>1091-604-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>551.54</v>
+        <v>13461.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1091-682-CM25</t>
+          <t>1091-640-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1138.62</v>
+        <v>551.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1091-694-CM25</t>
+          <t>1091-682-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7635.2</v>
+        <v>1138.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3708-27-CM26</t>
+          <t>1091-694-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,27 +951,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1916.5</v>
+        <v>7635.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3705-16-CM26</t>
+          <t>3708-27-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>634.5700000000001</v>
+        <v>1916.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1079659-16-CM26</t>
+          <t>3705-16-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.082.051-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4634.34</v>
+        <v>634.5700000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1523-120-CM26</t>
+          <t>1079659-16-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1017.71</v>
+        <v>4634.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3705-17-CM26</t>
+          <t>1523-120-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1027.98</v>
+        <v>1017.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3708-37-CM26</t>
+          <t>3705-17-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.511.768-2</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>5714.95</v>
+        <v>1027.98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3460-8-CM26</t>
+          <t>3708-37-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIALIZADORA expressVirtual SpA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.511.768-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6333.81</v>
+        <v>5714.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1091-23-CM26</t>
+          <t>3460-8-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>447.92</v>
+        <v>6333.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1175-132-CM26</t>
+          <t>1091-23-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1801.14</v>
+        <v>447.92</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3935-8-CM26</t>
+          <t>1175-132-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.607.400-8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13906.04</v>
+        <v>1801.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2546-115-CM26</t>
+          <t>3935-8-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4007.69</v>
+        <v>13906.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3153-43-CM26</t>
+          <t>2546-115-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.851.564-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4417.62</v>
+        <v>4007.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3477-161-CM26</t>
+          <t>3153-43-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1698,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>18506.36</v>
+        <v>4417.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3935-24-CM26</t>
+          <t>3477-161-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
+          <t>Fundacion Vivienda</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.141.693-6</t>
+          <t>70.016.130-7</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>46638.46</v>
+        <v>18506.36</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2387-125-CM26</t>
+          <t>3935-24-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.141.693-6</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1423.28</v>
+        <v>46638.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1078177-297-CM26</t>
+          <t>2387-125-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.730.550-8</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8423.790000000001</v>
+        <v>1423.28</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4284-196-CM26</t>
+          <t>1078177-297-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>60.505.522-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1839.59</v>
+        <v>8423.790000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1079659-182-CM26</t>
+          <t>4284-196-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,12 +2003,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9470.040000000001</v>
+        <v>1839.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3477-446-CM26</t>
+          <t>1079659-182-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>34224.65</v>
+        <v>9470.040000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4285-181-CM26</t>
+          <t>3477-446-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>872.62</v>
+        <v>34224.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1906-50-CM26</t>
+          <t>4285-181-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2176,22 +2176,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.002.022-4</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,6 +2216,67 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
+        <v>872.62</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1906-50-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.002.022-4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Servicio de Registro Civil e Identificación</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
         <v>3332.02</v>
       </c>
     </row>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Araucanía" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3887-242-CM25</t>
+          <t>3516-28-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1649.38</v>
+        <v>236.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>701426-405-CM25</t>
+          <t>3516-65-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.094.280-0</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25435.53</v>
+        <v>308.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1091-487-CM25</t>
+          <t>2546-35-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1348.41</v>
+        <v>3486.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1091-592-CM25</t>
+          <t>2546-74-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2998.18</v>
+        <v>6859.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1091-604-CM25</t>
+          <t>3153-40-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13461.71</v>
+        <v>5813.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1091-640-CM25</t>
+          <t>1091-278-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>551.54</v>
+        <v>2124.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1091-682-CM25</t>
+          <t>3887-242-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1138.62</v>
+        <v>1649.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1091-694-CM25</t>
+          <t>4284-231-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7635.2</v>
+        <v>1985.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3708-27-CM26</t>
+          <t>2546-456-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1916.5</v>
+        <v>17778.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3705-16-CM26</t>
+          <t>3887-315-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.082.051-0</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>634.5700000000001</v>
+        <v>2177.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1079659-16-CM26</t>
+          <t>3153-215-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4634.34</v>
+        <v>4865.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1523-120-CM26</t>
+          <t>2036-376-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.602.247-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>SERVICIO DE SALUD DE LA ARAUCANIA SUR HOSPITAL LONCOCHE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Hales Hnos y Cia Ltda</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>83.535.000-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1017.71</v>
+        <v>1124.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3705-17-CM26</t>
+          <t>3935-114-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>15.775.663-k</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1027.98</v>
+        <v>12412.43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3708-37-CM26</t>
+          <t>701426-262-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>COMERCIAL EL TORO SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.511.768-2</t>
+          <t>76.209.677-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5714.95</v>
+        <v>2438.22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3460-8-CM26</t>
+          <t>1079659-317-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1378,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>61.980.860-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6333.81</v>
+        <v>2278.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1091-23-CM26</t>
+          <t>3565-579-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,12 +1439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.252.100-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>447.92</v>
+        <v>4452.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1175-132-CM26</t>
+          <t>1091-414-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.607.400-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.325.352-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1801.14</v>
+        <v>2735.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3935-8-CM26</t>
+          <t>2546-795-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIAL ORIONIS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.721.492-6</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13906.04</v>
+        <v>5142.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2546-115-CM26</t>
+          <t>3460-281-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIAL SAN MARTIN SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.851.564-4</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>4007.69</v>
+        <v>5006.98</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3153-43-CM26</t>
+          <t>3890-329-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1683,27 +1683,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.141.693-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4417.62</v>
+        <v>1302.66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3477-161-CM26</t>
+          <t>3935-179-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1744,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
+          <t>76.141.693-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>18506.36</v>
+        <v>11205.43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3935-24-CM26</t>
+          <t>3460-320-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1805,27 +1805,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.141.693-6</t>
+          <t>76.299.358-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>46638.46</v>
+        <v>6425.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2387-125-CM26</t>
+          <t>3935-198-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.730.550-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1423.28</v>
+        <v>11108.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1078177-297-CM26</t>
+          <t>2546-908-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,27 +1927,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.505.522-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>15.888.842-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8423.790000000001</v>
+        <v>14922.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4284-196-CM26</t>
+          <t>701426-405-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1839.59</v>
+        <v>25435.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1079659-182-CM26</t>
+          <t>1091-487-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.980.860-6</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>9470.040000000001</v>
+        <v>1348.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3477-446-CM26</t>
+          <t>1091-592-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>34224.65</v>
+        <v>2998.18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4285-181-CM26</t>
+          <t>1091-604-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>872.62</v>
+        <v>13461.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1906-50-CM26</t>
+          <t>1091-640-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.002.022-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,7 +2277,1837 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
+        <v>551.54</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1091-682-CM25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>1138.62</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1091-694-CM25</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>7635.2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3708-27-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>1916.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3705-16-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOLUCIONES INTEGRALES EMERGENZA SPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>77.082.051-0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>634.5700000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1079659-16-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>4634.34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1523-120-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1017.71</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3705-17-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>69.180.300-7</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>1027.98</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3460-8-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>61.101.069-9</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ejercito de Chile</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>6333.81</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3708-37-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>69.191.300-7</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA expressVirtual SpA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>76.511.768-2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>5714.95</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1091-23-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>447.92</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1175-132-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.607.400-8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>1801.14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3935-8-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>13906.04</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2546-115-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>4007.69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3153-43-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>69.180.500-k</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>4417.62</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3477-161-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Fundacion Vivienda</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>18506.36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3935-24-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>76.141.693-6</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>46638.46</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2387-125-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>69.191.600-6</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUCON</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>DESARROLLOS ALIMENTICIOS S.A.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.730.550-8</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>1423.28</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1078177-297-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS IX ZONA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>8423.790000000001</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4284-196-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>1839.59</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1079659-182-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>9470.040000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3477-446-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>11.372.911-2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>34224.65</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4285-181-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>69.191.000-8</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>872.62</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1906-50-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.002.022-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Servicio de Registro Civil e Identificación</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
         <v>3332.02</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2103-476-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.607.402-4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hospital  Lonquimay</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>223.77</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3697-628-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>69.180.900-5</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>5812.97</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2736-272-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>15017.62</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2736-289-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>18617.97</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1658-2328-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>1219.53</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4179-1010-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>3264.15</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2548-519-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>559.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA expressVirtual SpA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Fundacion Vivienda</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA CARAB ARAUCANÍA CONT ORD PUBL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -745,7 +745,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1058,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1123,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1188,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1436,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1562,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1627,11 @@
           <t>77.721.492-6</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1692,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1879,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2005,11 @@
           <t>15.888.842-4</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>78.094.280-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2501,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2566,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2631,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2696,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2761,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2826,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3135,11 @@
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3200,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3448,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3513,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3578,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3765,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3830,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4139,11 @@
           <t>77.325.352-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2778,7 +2778,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3460-8-CM26</t>
+          <t>3708-37-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2798,17 +2798,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.101.069-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2818,32 +2818,28 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.299.358-9</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.511.768-2</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6333.81</v>
+        <v>5714.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3708-37-CM26</t>
+          <t>3460-8-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2863,17 +2859,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>61.101.069-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2883,22 +2879,26 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EXPRESSVIRTUAL SPA</t>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.511.768-2</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5714.95</v>
+        <v>6333.81</v>
       </c>
     </row>
     <row r="40">
@@ -3152,7 +3152,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3153-43-CM26</t>
+          <t>3477-161-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3192,32 +3192,28 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4417.62</v>
+        <v>18506.36</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3477-161-CM26</t>
+          <t>3153-43-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3242,12 +3238,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3257,22 +3253,26 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18506.36</v>
+        <v>4417.62</v>
       </c>
     </row>
     <row r="46">
@@ -3782,7 +3782,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2103-476-CM26</t>
+          <t>3697-628-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3807,12 +3807,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3822,32 +3822,28 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>223.77</v>
+        <v>5812.97</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3697-628-CM26</t>
+          <t>2103-476-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3872,12 +3868,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>61.607.402-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>Hospital  Lonquimay</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3887,22 +3883,26 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5812.97</v>
+        <v>223.77</v>
       </c>
     </row>
     <row r="56">
@@ -4212,6 +4212,136 @@
       </c>
       <c r="M60" s="2" t="n">
         <v>559.36</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2103-631-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.607.402-4</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Hospital  Lonquimay</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>214.17</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2546-963-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>COMERCIAL SAN MARTIN SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>77.851.564-4</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>33141.83</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -3615,7 +3615,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">

--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M62"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3152,7 +3152,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3477-161-CM26</t>
+          <t>3153-43-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3192,28 +3192,32 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>FUNDACION VIVIENDA</t>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>70.016.130-7</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>18506.36</v>
+        <v>4417.62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3153-43-CM26</t>
+          <t>3477-161-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3238,12 +3242,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3253,26 +3257,22 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>FUNDACION VIVIENDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>70.016.130-7</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4417.62</v>
+        <v>18506.36</v>
       </c>
     </row>
     <row r="46">
@@ -4217,7 +4217,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2103-631-CM26</t>
+          <t>3935-175-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4237,17 +4237,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4257,90 +4257,151 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>214.17</v>
+        <v>9269.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>2103-631-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.607.402-4</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Hospital  Lonquimay</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>214.17</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>2546-963-CM26</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2239-8-LR24</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>61.955.000-5</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
         <is>
           <t>COMERCIAL SAN MARTIN SPA</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>77.851.564-4</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="n">
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
         <v>33141.83</v>
       </c>
     </row>
